--- a/Packages/cn.etetet.twsmmo/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Base/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -84,6 +84,66 @@
   </si>
   <si>
     <t>注释</t>
+  </si>
+  <si>
+    <t>cn.etetet.twsmmo.SelectType</t>
+  </si>
+  <si>
+    <t>OneWithInRange</t>
+  </si>
+  <si>
+    <t>单个</t>
+  </si>
+  <si>
+    <t>范围内距离最近的一个</t>
+  </si>
+  <si>
+    <t>Circular</t>
+  </si>
+  <si>
+    <t>圆形</t>
+  </si>
+  <si>
+    <t>圆形区域内所有</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>扇形</t>
+  </si>
+  <si>
+    <t>扇形区域内所有</t>
+  </si>
+  <si>
+    <t>cn.etetet.twsmmo.ActionType</t>
+  </si>
+  <si>
+    <t>NumericChange</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>改变目标数值，如果是buff，删除会还原数值</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>伤害</t>
+  </si>
+  <si>
+    <t>造成伤害</t>
+  </si>
+  <si>
+    <t>CastBullet</t>
+  </si>
+  <si>
+    <t>子弹</t>
+  </si>
+  <si>
+    <t>创建子弹</t>
   </si>
 </sst>
 </file>
@@ -1046,11 +1106,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25" outlineLevelRow="2"/>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
-    <col min="2" max="12" width="16.875" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="10" width="16.875" customWidth="1"/>
+    <col min="11" max="11" width="21.25" customWidth="1"/>
+    <col min="12" max="12" width="16.875" customWidth="1"/>
     <col min="13" max="16384" width="7.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1139,6 +1202,108 @@
         <v>18</v>
       </c>
       <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="8:11">
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="8:11">
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="2:11">
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="8:11">
+      <c r="H8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="8:11">
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Base/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -86,39 +86,12 @@
     <t>注释</t>
   </si>
   <si>
-    <t>cn.etetet.twsmmo.SelectType</t>
-  </si>
-  <si>
-    <t>OneWithInRange</t>
-  </si>
-  <si>
-    <t>单个</t>
-  </si>
-  <si>
-    <t>范围内距离最近的一个</t>
-  </si>
-  <si>
-    <t>Circular</t>
-  </si>
-  <si>
-    <t>圆形</t>
-  </si>
-  <si>
-    <t>圆形区域内所有</t>
-  </si>
-  <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>扇形</t>
-  </si>
-  <si>
-    <t>扇形区域内所有</t>
-  </si>
-  <si>
     <t>cn.etetet.twsmmo.ActionType</t>
   </si>
   <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>NumericChange</t>
   </si>
   <si>
@@ -137,13 +110,79 @@
     <t>造成伤害</t>
   </si>
   <si>
-    <t>CastBullet</t>
-  </si>
-  <si>
-    <t>子弹</t>
-  </si>
-  <si>
-    <t>创建子弹</t>
+    <t>CreateCast</t>
+  </si>
+  <si>
+    <t>创建技能</t>
+  </si>
+  <si>
+    <t>CastBuff</t>
+  </si>
+  <si>
+    <t>创建Buff</t>
+  </si>
+  <si>
+    <t>CastParticle</t>
+  </si>
+  <si>
+    <t>创建特效</t>
+  </si>
+  <si>
+    <t>DirLineMove</t>
+  </si>
+  <si>
+    <t>移动方向直线移动</t>
+  </si>
+  <si>
+    <t>ForwardLineMove</t>
+  </si>
+  <si>
+    <t>正前方直线移动</t>
+  </si>
+  <si>
+    <t>CurveMove</t>
+  </si>
+  <si>
+    <t>曲线移动</t>
+  </si>
+  <si>
+    <t>RandomPos</t>
+  </si>
+  <si>
+    <t>随机位置</t>
+  </si>
+  <si>
+    <t>RandomDirLineMove</t>
+  </si>
+  <si>
+    <t>随机方向直线移动</t>
+  </si>
+  <si>
+    <t>cn.etetet.twsmmo.CastType</t>
+  </si>
+  <si>
+    <t>ActiveCast</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+  </si>
+  <si>
+    <t>PassiveCast</t>
+  </si>
+  <si>
+    <t>被动技能</t>
+  </si>
+  <si>
+    <t>AuxiliaryCast</t>
+  </si>
+  <si>
+    <t>辅助技能</t>
+  </si>
+  <si>
+    <t>CastLevelUp</t>
+  </si>
+  <si>
+    <t>技能升级</t>
   </si>
 </sst>
 </file>
@@ -1106,13 +1145,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="10" width="16.875" customWidth="1"/>
-    <col min="11" max="11" width="21.25" customWidth="1"/>
+    <col min="3" max="7" width="16.875" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="10" width="16.875" customWidth="1"/>
+    <col min="11" max="11" width="75.375" customWidth="1"/>
     <col min="12" max="12" width="16.875" customWidth="1"/>
     <col min="13" max="16384" width="7.75" customWidth="1"/>
   </cols>
@@ -1203,7 +1244,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" customFormat="1" spans="2:11">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1213,39 +1254,42 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="8:11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="8:11">
       <c r="H5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="8:11">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="8:11">
       <c r="H6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -1254,55 +1298,170 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="2:11">
-      <c r="B7" t="s">
+    <row r="7" spans="8:11">
+      <c r="H7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" t="b">
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="8:11">
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="8:11">
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="8:11">
+      <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
+      <c r="K10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="8:11">
+      <c r="H11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11">
+        <v>7</v>
+      </c>
+      <c r="K11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="8:11">
+      <c r="H12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12">
+        <v>8</v>
+      </c>
+      <c r="K12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="8:11">
+      <c r="H13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13">
+        <v>9</v>
+      </c>
+      <c r="K13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="b">
         <v>0</v>
       </c>
-      <c r="D7" t="b">
+      <c r="D14" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7">
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14">
         <v>0</v>
       </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="8:11">
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8">
+      <c r="K14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="8:11">
+      <c r="H15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15">
         <v>1</v>
       </c>
-      <c r="K8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="8:11">
-      <c r="H9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9">
+      <c r="K15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="8:11">
+      <c r="H16" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16">
         <v>2</v>
       </c>
-      <c r="K9" t="s">
-        <v>38</v>
+      <c r="K16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="8:11">
+      <c r="H17" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" t="s">
+        <v>51</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Base/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -156,6 +156,33 @@
   </si>
   <si>
     <t>随机方向直线移动</t>
+  </si>
+  <si>
+    <t>HitDestroySelf</t>
+  </si>
+  <si>
+    <t>碰撞销毁自身</t>
+  </si>
+  <si>
+    <t>UpParabola</t>
+  </si>
+  <si>
+    <t>向上抛物线</t>
+  </si>
+  <si>
+    <t>HitRotate</t>
+  </si>
+  <si>
+    <t>碰撞转向</t>
+  </si>
+  <si>
+    <t>AutoDispose</t>
+  </si>
+  <si>
+    <t>自动销毁</t>
+  </si>
+  <si>
+    <t>技能持续时间结束，自动销毁</t>
   </si>
   <si>
     <t>cn.etetet.twsmmo.CastType</t>
@@ -348,12 +375,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -689,7 +722,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -713,16 +746,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -731,99 +764,102 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1145,7 +1181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -1159,90 +1195,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="1"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" customFormat="1" spans="2:11">
       <c r="B4" t="s">
@@ -1396,72 +1432,133 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:11">
-      <c r="B14" t="s">
+    <row r="14" spans="8:11">
+      <c r="H14" t="s">
         <v>43</v>
       </c>
-      <c r="C14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>44</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14">
+        <v>10</v>
+      </c>
+      <c r="K14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="8:11">
+      <c r="H15" t="s">
         <v>45</v>
       </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="8:11">
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>46</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15">
+        <v>11</v>
+      </c>
+      <c r="K15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="8:11">
+      <c r="H16" t="s">
         <v>47</v>
       </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="8:11">
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>48</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16">
+        <v>12</v>
+      </c>
+      <c r="K16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="8:11">
+      <c r="H17" t="s">
         <v>49</v>
       </c>
-      <c r="J16">
-        <v>2</v>
-      </c>
-      <c r="K16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="8:11">
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>50</v>
       </c>
-      <c r="I17" t="s">
-        <v>51</v>
-      </c>
       <c r="J17">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K17" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="8:11">
+      <c r="H20" t="s">
+        <v>55</v>
+      </c>
+      <c r="I20" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="8:11">
+      <c r="H21" t="s">
+        <v>57</v>
+      </c>
+      <c r="I21" t="s">
+        <v>58</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="8:11">
+      <c r="H22" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+      <c r="K22" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Base/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -183,6 +183,30 @@
   </si>
   <si>
     <t>技能持续时间结束，自动销毁</t>
+  </si>
+  <si>
+    <t>ManeuverMove</t>
+  </si>
+  <si>
+    <t>回旋移动</t>
+  </si>
+  <si>
+    <t>SetPos</t>
+  </si>
+  <si>
+    <t>设置位置</t>
+  </si>
+  <si>
+    <t>SetPosByParent</t>
+  </si>
+  <si>
+    <t>根据父级设置位置</t>
+  </si>
+  <si>
+    <t>MoveToMouse</t>
+  </si>
+  <si>
+    <t>向鼠标位置移动</t>
   </si>
   <si>
     <t>cn.etetet.twsmmo.CastType</t>
@@ -1181,7 +1205,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -1488,77 +1512,133 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="1:1">
-      <c r="A18" s="1" t="s">
+    <row r="18" customFormat="1" spans="8:11">
+      <c r="H18" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18">
+        <v>14</v>
+      </c>
+      <c r="K18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="8:11">
+      <c r="H19" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19">
+        <v>15</v>
+      </c>
+      <c r="K19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="8:11">
+      <c r="H20" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" t="s">
+        <v>57</v>
+      </c>
+      <c r="J20">
+        <v>16</v>
+      </c>
+      <c r="K20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="8:11">
+      <c r="H21" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21">
+        <v>17</v>
+      </c>
+      <c r="K21" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:1">
+      <c r="A22" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="2:11">
-      <c r="B19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" t="b">
+    <row r="23" spans="2:11">
+      <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="b">
         <v>0</v>
       </c>
-      <c r="D19" t="b">
+      <c r="D23" t="b">
         <v>1</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E23" t="s">
         <v>20</v>
       </c>
-      <c r="H19" t="s">
-        <v>53</v>
-      </c>
-      <c r="I19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J19">
+      <c r="H23" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" t="s">
+        <v>62</v>
+      </c>
+      <c r="J23">
         <v>0</v>
       </c>
-      <c r="K19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="8:11">
-      <c r="H20" t="s">
-        <v>55</v>
-      </c>
-      <c r="I20" t="s">
-        <v>56</v>
-      </c>
-      <c r="J20">
+      <c r="K23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="8:11">
+      <c r="H24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24">
         <v>1</v>
       </c>
-      <c r="K20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="8:11">
-      <c r="H21" t="s">
-        <v>57</v>
-      </c>
-      <c r="I21" t="s">
-        <v>58</v>
-      </c>
-      <c r="J21">
+      <c r="K24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="8:11">
+      <c r="H25" t="s">
+        <v>65</v>
+      </c>
+      <c r="I25" t="s">
+        <v>66</v>
+      </c>
+      <c r="J25">
         <v>2</v>
       </c>
-      <c r="K21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="8:11">
-      <c r="H22" t="s">
-        <v>59</v>
-      </c>
-      <c r="I22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J22">
+      <c r="K25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="8:11">
+      <c r="H26" t="s">
+        <v>67</v>
+      </c>
+      <c r="I26" t="s">
+        <v>68</v>
+      </c>
+      <c r="J26">
         <v>3</v>
       </c>
-      <c r="K22" t="s">
-        <v>60</v>
+      <c r="K26" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twsmmo/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twsmmo/Luban/Config/Base/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -209,6 +209,12 @@
     <t>向鼠标位置移动</t>
   </si>
   <si>
+    <t>MoveToPlayer</t>
+  </si>
+  <si>
+    <t>向玩家移动</t>
+  </si>
+  <si>
     <t>cn.etetet.twsmmo.CastType</t>
   </si>
   <si>
@@ -224,16 +230,13 @@
     <t>被动技能</t>
   </si>
   <si>
-    <t>AuxiliaryCast</t>
-  </si>
-  <si>
-    <t>辅助技能</t>
-  </si>
-  <si>
-    <t>CastLevelUp</t>
-  </si>
-  <si>
-    <t>技能升级</t>
+    <t>OnceCast</t>
+  </si>
+  <si>
+    <t>一次性技能</t>
+  </si>
+  <si>
+    <t>一次性技能，针对当前某个技能进行数据调整</t>
   </si>
 </sst>
 </file>
@@ -1568,38 +1571,38 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="1:1">
-      <c r="A22" s="1" t="s">
+    <row r="22" customFormat="1" spans="8:11">
+      <c r="H22" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22">
+        <v>18</v>
+      </c>
+      <c r="K22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:1">
+      <c r="A23" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="2:11">
-      <c r="B23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" t="b">
+    <row r="24" spans="2:11">
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" t="b">
         <v>0</v>
       </c>
-      <c r="D23" t="b">
+      <c r="D24" t="b">
         <v>1</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E24" t="s">
         <v>20</v>
       </c>
-      <c r="H23" t="s">
-        <v>61</v>
-      </c>
-      <c r="I23" t="s">
-        <v>62</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="8:11">
       <c r="H24" t="s">
         <v>63</v>
       </c>
@@ -1607,7 +1610,7 @@
         <v>64</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="s">
         <v>64</v>
@@ -1621,7 +1624,7 @@
         <v>66</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" t="s">
         <v>66</v>
@@ -1635,10 +1638,10 @@
         <v>68</v>
       </c>
       <c r="J26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
